--- a/branches/fix/invariant-fhirpath-aliases/StructureDefinition-mii-pr-icu-score-wong-baker-faces-schmerzskala.xlsx
+++ b/branches/fix/invariant-fhirpath-aliases/StructureDefinition-mii-pr-icu-score-wong-baker-faces-schmerzskala.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T12:10:38+00:00</t>
+    <t>2026-09-15T13:25:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
